--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,164 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43555</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
+        <v>100</v>
+      </c>
+      <c r="G8" s="3">
         <v>200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>300</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3">
         <v>200</v>
       </c>
       <c r="K8" s="3">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3">
+        <v>200</v>
+      </c>
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
-      </c>
-      <c r="O8" s="3">
-        <v>100</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
+      <c r="R8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,8 +887,14 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -936,8 +955,14 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,8 +985,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1004,26 +1031,32 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1117,14 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1146,8 +1185,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1253,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1280,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>2400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2100</v>
       </c>
       <c r="M17" s="3">
         <v>2500</v>
       </c>
       <c r="N17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="O17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="P17" s="3">
         <v>2400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1500</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3">
         <v>-2800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,20 +1442,22 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1418,111 +1485,123 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="R20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3">
         <v>-2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-2100</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1540,17 +1619,17 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1563,8 +1642,14 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1575,58 +1660,64 @@
         <v>-900</v>
       </c>
       <c r="F23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-5100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-2100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1687,8 +1778,14 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,8 +1846,14 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1761,58 +1864,64 @@
         <v>-900</v>
       </c>
       <c r="F26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-2100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1823,58 +1932,64 @@
         <v>-900</v>
       </c>
       <c r="F27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +2050,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2118,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2186,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,20 +2254,26 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2162,29 +2301,35 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="R32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2195,58 +2340,64 @@
         <v>-900</v>
       </c>
       <c r="F33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,8 +2458,14 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2319,125 +2476,137 @@
         <v>-900</v>
       </c>
       <c r="F35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43555</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2629,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,59 +2655,61 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F41" s="3">
         <v>5400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>10600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>12100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>13700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>16400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,8 +2719,14 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2608,8 +2787,14 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2620,17 +2805,17 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>100</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
         <v>0</v>
       </c>
@@ -2638,29 +2823,29 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,8 +2855,14 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2732,58 +2923,64 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
-        <v>200</v>
-      </c>
       <c r="F45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
       </c>
       <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1100</v>
-      </c>
-      <c r="O45" s="3">
-        <v>100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>200</v>
+      </c>
+      <c r="S45" s="3">
+        <v>100</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2794,59 +2991,65 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F46" s="3">
         <v>5500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>6300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>8300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>7700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>9500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>12800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>14800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>16800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>4400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3400</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,8 +3059,14 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2918,8 +3127,14 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2960,16 +3175,16 @@
         <v>100</v>
       </c>
       <c r="P48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>0</v>
+      </c>
+      <c r="S48" s="3">
+        <v>100</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -2980,58 +3195,64 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>700</v>
+      </c>
+      <c r="F49" s="3">
         <v>800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1200</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1300</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1300</v>
       </c>
       <c r="L49" s="3">
         <v>1300</v>
       </c>
       <c r="M49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="N49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="O49" s="3">
         <v>1400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>1400</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1300</v>
       </c>
       <c r="Q49" s="3">
         <v>1300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S49" s="3">
+        <v>1300</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3042,8 +3263,14 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3331,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3399,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3207,8 +3446,8 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3216,8 +3455,8 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3228,8 +3467,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,59 +3535,65 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F54" s="3">
         <v>6300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>7300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>12200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>12500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>14200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>16300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>18200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>5700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>4800</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3603,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3633,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,8 +3659,10 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3415,22 +3676,22 @@
         <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
         <v>400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
@@ -3439,19 +3700,19 @@
         <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>400</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>100</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3462,8 +3723,14 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3504,14 +3771,14 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>2000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3524,59 +3791,65 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E59" s="3">
         <v>200</v>
       </c>
       <c r="F59" s="3">
+        <v>200</v>
+      </c>
+      <c r="G59" s="3">
+        <v>200</v>
+      </c>
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,59 +3859,65 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E60" s="3">
         <v>300</v>
       </c>
       <c r="F60" s="3">
+        <v>300</v>
+      </c>
+      <c r="G60" s="3">
+        <v>300</v>
+      </c>
+      <c r="H60" s="3">
         <v>400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3927,14 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3710,8 +3995,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3772,8 +4063,14 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +4131,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4199,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,59 +4267,65 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E66" s="3">
         <v>300</v>
       </c>
       <c r="F66" s="3">
+        <v>300</v>
+      </c>
+      <c r="G66" s="3">
+        <v>300</v>
+      </c>
+      <c r="H66" s="3">
         <v>400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>600</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4335,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4365,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4429,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4497,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4230,8 +4565,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,59 +4633,65 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-33400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-32500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-31600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-30900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-29300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-27100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-24900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-20200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-18300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-16000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-13700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-7200</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4701,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4769,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4837,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,59 +4905,65 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F76" s="3">
         <v>6100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>7000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>9200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>11100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>15300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>16600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>4200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4973,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,75 +5041,87 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43555</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4743,58 +5132,64 @@
         <v>-900</v>
       </c>
       <c r="F81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,13 +5212,15 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -4862,25 +5259,31 @@
         <v>200</v>
       </c>
       <c r="Q83" s="3">
+        <v>200</v>
+      </c>
+      <c r="R83" s="3">
+        <v>200</v>
+      </c>
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5344,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5412,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5480,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5548,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5616,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-700</v>
+        <v>-900</v>
       </c>
       <c r="E89" s="3">
         <v>-700</v>
       </c>
       <c r="F89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,8 +5714,10 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5299,19 +5740,19 @@
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5328,17 +5769,23 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5846,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,8 +5914,14 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5485,16 +5944,16 @@
         <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-200</v>
       </c>
       <c r="M94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="N94" s="3">
         <v>-200</v>
@@ -5503,28 +5962,34 @@
         <v>-200</v>
       </c>
       <c r="P94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +6012,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +6076,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +6144,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +6212,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,8 +6280,14 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5810,55 +6301,61 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>12800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>4800</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5919,66 +6416,78 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>12300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>1900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-2200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,109 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -766,22 +770,22 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3">
         <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
+        <v>200</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
@@ -790,34 +794,34 @@
         <v>200</v>
       </c>
       <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
-      </c>
-      <c r="P8" s="3">
-        <v>100</v>
       </c>
       <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
+      <c r="V8" s="3">
+        <v>0</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
@@ -825,8 +829,11 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -893,8 +900,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,8 +1000,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,26 +1051,29 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U12" s="3">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1191,8 +1211,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,76 +1308,80 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E17" s="3">
         <v>1000</v>
       </c>
       <c r="F17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2500</v>
       </c>
       <c r="M17" s="3">
         <v>2500</v>
       </c>
       <c r="N17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="O17" s="3">
         <v>2100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2200</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,67 +1389,70 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-1000</v>
       </c>
       <c r="G18" s="3">
         <v>-1000</v>
       </c>
       <c r="H18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-2300</v>
       </c>
       <c r="P18" s="3">
         <v>-2300</v>
       </c>
       <c r="Q18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2200</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1477,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1453,14 +1487,14 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1491,11 +1525,11 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1503,8 +1537,8 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1512,8 +1546,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1521,67 +1558,70 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-700</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-800</v>
       </c>
       <c r="G21" s="3">
         <v>-800</v>
       </c>
       <c r="H21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-2100</v>
       </c>
       <c r="P21" s="3">
         <v>-2100</v>
       </c>
       <c r="Q21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>-2400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2100</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1591,8 +1631,8 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1600,11 +1640,11 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1625,14 +1665,14 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>3600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1648,13 +1688,16 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E23" s="3">
         <v>-900</v>
@@ -1666,58 +1709,61 @@
         <v>-900</v>
       </c>
       <c r="H23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-2300</v>
       </c>
       <c r="P23" s="3">
         <v>-2300</v>
       </c>
       <c r="Q23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R23" s="3">
         <v>-5100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1784,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,13 +1901,16 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E26" s="3">
         <v>-900</v>
@@ -1870,63 +1922,66 @@
         <v>-900</v>
       </c>
       <c r="H26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-2300</v>
       </c>
       <c r="P26" s="3">
         <v>-2300</v>
       </c>
       <c r="Q26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R26" s="3">
         <v>-5100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E27" s="3">
         <v>-900</v>
@@ -1938,58 +1993,61 @@
         <v>-900</v>
       </c>
       <c r="H27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-2300</v>
       </c>
       <c r="P27" s="3">
         <v>-2300</v>
       </c>
       <c r="Q27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R27" s="3">
         <v>-5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2327,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2269,14 +2339,14 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2307,11 +2377,11 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -2319,8 +2389,8 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2328,13 +2398,16 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E33" s="3">
         <v>-900</v>
@@ -2346,58 +2419,61 @@
         <v>-900</v>
       </c>
       <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-2300</v>
       </c>
       <c r="P33" s="3">
         <v>-2300</v>
       </c>
       <c r="Q33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R33" s="3">
         <v>-5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,13 +2540,16 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E35" s="3">
         <v>-900</v>
@@ -2482,131 +2561,137 @@
         <v>-900</v>
       </c>
       <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-2300</v>
       </c>
       <c r="P35" s="3">
         <v>-2300</v>
       </c>
       <c r="Q35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R35" s="3">
         <v>-5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,62 +2743,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,8 +2812,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2793,8 +2883,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2811,13 +2904,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I43" s="3">
         <v>100</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2829,26 +2922,26 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2861,8 +2954,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2929,8 +3025,11 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2938,53 +3037,53 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
       </c>
       <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
         <v>200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>600</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
       </c>
       <c r="L45" s="3">
+        <v>600</v>
+      </c>
+      <c r="M45" s="3">
         <v>800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,62 +3096,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E46" s="3">
         <v>3900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,8 +3167,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3133,8 +3238,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3181,14 +3289,14 @@
         <v>100</v>
       </c>
       <c r="R48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S48" s="3">
+        <v>0</v>
+      </c>
+      <c r="T48" s="3">
         <v>100</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,8 +3309,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3210,28 +3321,28 @@
         <v>600</v>
       </c>
       <c r="E49" s="3">
+        <v>600</v>
+      </c>
+      <c r="F49" s="3">
         <v>700</v>
-      </c>
-      <c r="F49" s="3">
-        <v>800</v>
       </c>
       <c r="G49" s="3">
         <v>800</v>
       </c>
       <c r="H49" s="3">
+        <v>800</v>
+      </c>
+      <c r="I49" s="3">
         <v>900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1200</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1300</v>
       </c>
       <c r="M49" s="3">
         <v>1300</v>
@@ -3240,13 +3351,13 @@
         <v>1300</v>
       </c>
       <c r="O49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="P49" s="3">
         <v>1400</v>
       </c>
       <c r="Q49" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="R49" s="3">
         <v>1300</v>
@@ -3254,8 +3365,8 @@
       <c r="S49" s="3">
         <v>1300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>1300</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,8 +3522,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3452,14 +3572,14 @@
       <c r="Q52" s="3">
         <v>0</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,62 +3664,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E54" s="3">
         <v>4600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>12500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4800</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,8 +3791,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3682,40 +3813,40 @@
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>400</v>
-      </c>
-      <c r="L57" s="3">
-        <v>200</v>
       </c>
       <c r="M57" s="3">
         <v>200</v>
       </c>
       <c r="N57" s="3">
+        <v>200</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>400</v>
-      </c>
-      <c r="R57" s="3">
-        <v>100</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>100</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3729,8 +3860,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3777,11 +3911,11 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>2000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,8 +3931,11 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3806,7 +3943,7 @@
         <v>100</v>
       </c>
       <c r="E59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
         <v>200</v>
@@ -3815,44 +3952,44 @@
         <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +4002,11 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3874,7 +4014,7 @@
         <v>200</v>
       </c>
       <c r="E60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F60" s="3">
         <v>300</v>
@@ -3883,44 +4023,44 @@
         <v>300</v>
       </c>
       <c r="H60" s="3">
+        <v>300</v>
+      </c>
+      <c r="I60" s="3">
         <v>400</v>
-      </c>
-      <c r="I60" s="3">
-        <v>700</v>
       </c>
       <c r="J60" s="3">
         <v>700</v>
       </c>
       <c r="K60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L60" s="3">
         <v>800</v>
       </c>
       <c r="M60" s="3">
+        <v>800</v>
+      </c>
+      <c r="N60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1000</v>
       </c>
       <c r="P60" s="3">
         <v>1000</v>
       </c>
       <c r="Q60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,8 +4073,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4001,8 +4144,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4069,8 +4215,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,8 +4428,11 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4282,7 +4440,7 @@
         <v>200</v>
       </c>
       <c r="E66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F66" s="3">
         <v>300</v>
@@ -4291,44 +4449,44 @@
         <v>300</v>
       </c>
       <c r="H66" s="3">
+        <v>300</v>
+      </c>
+      <c r="I66" s="3">
         <v>400</v>
-      </c>
-      <c r="I66" s="3">
-        <v>700</v>
       </c>
       <c r="J66" s="3">
         <v>700</v>
       </c>
       <c r="K66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="L66" s="3">
         <v>800</v>
       </c>
       <c r="M66" s="3">
+        <v>800</v>
+      </c>
+      <c r="N66" s="3">
         <v>1100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>700</v>
-      </c>
-      <c r="O66" s="3">
-        <v>1000</v>
       </c>
       <c r="P66" s="3">
         <v>1000</v>
       </c>
       <c r="Q66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,62 +4810,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-35200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-34300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-33400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-32500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-31600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-30900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-29300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-27100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-24900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-20200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-13700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-7200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,62 +5094,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>9200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,86 +5236,92 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-900</v>
+        <v>-1400</v>
       </c>
       <c r="E81" s="3">
         <v>-900</v>
@@ -5138,58 +5333,61 @@
         <v>-900</v>
       </c>
       <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-2300</v>
       </c>
       <c r="P81" s="3">
         <v>-2300</v>
       </c>
       <c r="Q81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R81" s="3">
         <v>-5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5223,7 +5422,7 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
         <v>200</v>
@@ -5265,16 +5464,16 @@
         <v>200</v>
       </c>
       <c r="S83" s="3">
+        <v>200</v>
+      </c>
+      <c r="T83" s="3">
         <v>400</v>
-      </c>
-      <c r="T83" s="3">
-        <v>100</v>
       </c>
       <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
+      <c r="V83" s="3">
+        <v>100</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
@@ -5282,8 +5481,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,16 +5836,19 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-700</v>
       </c>
       <c r="F89" s="3">
         <v>-700</v>
@@ -5640,58 +5857,61 @@
         <v>-700</v>
       </c>
       <c r="H89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-1200</v>
       </c>
       <c r="N89" s="3">
         <v>-1200</v>
       </c>
       <c r="O89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,8 +5936,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5746,17 +5967,17 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -5775,8 +5996,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -5784,8 +6005,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,8 +6147,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5950,13 +6180,13 @@
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
       </c>
       <c r="O94" s="3">
         <v>-200</v>
@@ -5968,28 +6198,31 @@
         <v>-200</v>
       </c>
       <c r="R94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,8 +6529,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6307,23 +6553,23 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>2500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>1400</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
         <v>0</v>
       </c>
@@ -6331,22 +6577,22 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>12800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4800</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
@@ -6354,8 +6600,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6422,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,113 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -773,67 +781,73 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
         <v>100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>300</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
       </c>
       <c r="L8" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M8" s="3">
         <v>200</v>
       </c>
       <c r="N8" s="3">
+        <v>200</v>
+      </c>
+      <c r="O8" s="3">
+        <v>200</v>
+      </c>
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>100</v>
-      </c>
-      <c r="R8" s="3">
-        <v>100</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
-        <v>0</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -903,31 +917,37 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>200</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -974,8 +994,14 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,31 +1027,33 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>300</v>
+      </c>
+      <c r="J12" s="3">
+        <v>300</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -1054,26 +1082,32 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3">
         <v>100</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,31 +1177,37 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1214,8 +1254,14 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1238,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1285,8 +1331,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1361,164 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F17" s="3">
         <v>1500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>2400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2500</v>
-      </c>
-      <c r="O17" s="3">
-        <v>2100</v>
       </c>
       <c r="P17" s="3">
         <v>2500</v>
       </c>
       <c r="Q17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S17" s="3">
         <v>2400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-900</v>
       </c>
       <c r="E18" s="3">
-        <v>-1000</v>
+        <v>-1200</v>
       </c>
       <c r="F18" s="3">
-        <v>-900</v>
+        <v>-1500</v>
       </c>
       <c r="G18" s="3">
         <v>-1000</v>
       </c>
       <c r="H18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-2100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-2200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,25 +1544,27 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1528,100 +1596,112 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-900</v>
       </c>
       <c r="E21" s="3">
-        <v>-800</v>
+        <v>-1200</v>
       </c>
       <c r="F21" s="3">
-        <v>-700</v>
+        <v>-1500</v>
       </c>
       <c r="G21" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="H21" s="3">
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="I21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-2200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1300</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>-2400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-2100</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1634,11 +1714,11 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1649,8 +1729,8 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1668,17 +1748,17 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>3600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1691,19 +1771,25 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-900</v>
       </c>
       <c r="G23" s="3">
         <v>-900</v>
@@ -1712,81 +1798,87 @@
         <v>-900</v>
       </c>
       <c r="I23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-5100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-2100</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1833,8 +1925,14 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,19 +2002,25 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-900</v>
       </c>
       <c r="G26" s="3">
         <v>-900</v>
@@ -1925,69 +2029,75 @@
         <v>-900</v>
       </c>
       <c r="I26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-900</v>
       </c>
       <c r="G27" s="3">
         <v>-900</v>
@@ -1996,58 +2106,64 @@
         <v>-900</v>
       </c>
       <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2233,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2310,14 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2387,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,25 +2464,31 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2380,40 +2520,46 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-900</v>
       </c>
       <c r="G33" s="3">
         <v>-900</v>
@@ -2422,58 +2568,64 @@
         <v>-900</v>
       </c>
       <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,19 +2695,25 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-900</v>
       </c>
       <c r="G35" s="3">
         <v>-900</v>
@@ -2564,134 +2722,146 @@
         <v>-900</v>
       </c>
       <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2887,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,68 +2916,70 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4600</v>
       </c>
-      <c r="G41" s="3">
-        <v>5400</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J41" s="3">
         <v>6100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>10700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>13700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>16400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2989,14 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,38 +3066,44 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2925,29 +3111,29 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,31 +3143,37 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3028,67 +3220,73 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="M45" s="3">
+        <v>600</v>
+      </c>
+      <c r="N45" s="3">
+        <v>600</v>
+      </c>
+      <c r="O45" s="3">
+        <v>800</v>
+      </c>
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
-      </c>
-      <c r="H45" s="3">
-        <v>200</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="J45" s="3">
-        <v>200</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="R45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
-        <v>600</v>
-      </c>
-      <c r="M45" s="3">
-        <v>800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
-      </c>
-      <c r="P45" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>200</v>
+      </c>
+      <c r="V45" s="3">
+        <v>100</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
@@ -3099,68 +3297,74 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F46" s="3">
         <v>3200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>7400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>8500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>10800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>11100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>14800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>16800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,31 +3374,37 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3241,8 +3451,14 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3292,16 +3508,16 @@
         <v>100</v>
       </c>
       <c r="S48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T48" s="3">
         <v>100</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+      <c r="V48" s="3">
+        <v>100</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3312,67 +3528,73 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E49" s="3">
         <v>600</v>
       </c>
       <c r="F49" s="3">
+        <v>600</v>
+      </c>
+      <c r="G49" s="3">
+        <v>600</v>
+      </c>
+      <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1200</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1300</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1300</v>
       </c>
       <c r="O49" s="3">
         <v>1300</v>
       </c>
       <c r="P49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R49" s="3">
         <v>1400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1400</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1300</v>
       </c>
       <c r="T49" s="3">
         <v>1300</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>1300</v>
+      </c>
+      <c r="V49" s="3">
+        <v>1300</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3383,8 +3605,14 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3682,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,31 +3759,37 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3575,8 +3815,8 @@
       <c r="R52" s="3">
         <v>0</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -3584,8 +3824,8 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>0</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3596,8 +3836,14 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,68 +3913,74 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F54" s="3">
         <v>3800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>7300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>8300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>10000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>12200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>12500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>14200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>16300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>18200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4800</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3990,14 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +4023,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,8 +4052,10 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3801,7 +4063,7 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3">
         <v>100</v>
@@ -3816,22 +4078,22 @@
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
       </c>
       <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -3840,19 +4102,19 @@
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>100</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>100</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3863,8 +4125,14 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3914,14 +4182,14 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>2000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3934,68 +4202,74 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
-        <v>200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>200</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,68 +4279,74 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>800</v>
+      </c>
+      <c r="F60" s="3">
         <v>200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>200</v>
-      </c>
-      <c r="F60" s="3">
-        <v>300</v>
-      </c>
-      <c r="G60" s="3">
-        <v>300</v>
       </c>
       <c r="H60" s="3">
         <v>300</v>
       </c>
       <c r="I60" s="3">
+        <v>300</v>
+      </c>
+      <c r="J60" s="3">
+        <v>300</v>
+      </c>
+      <c r="K60" s="3">
         <v>400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,8 +4356,14 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4147,31 +4433,37 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4218,8 +4510,14 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4587,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4664,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,68 +4741,74 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>800</v>
+      </c>
+      <c r="F66" s="3">
         <v>200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>200</v>
-      </c>
-      <c r="F66" s="3">
-        <v>300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>300</v>
       </c>
       <c r="H66" s="3">
         <v>300</v>
       </c>
       <c r="I66" s="3">
+        <v>300</v>
+      </c>
+      <c r="J66" s="3">
+        <v>300</v>
+      </c>
+      <c r="K66" s="3">
         <v>400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>2700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4818,14 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4851,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4924,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +5001,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +5078,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,68 +5155,74 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-36700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-35200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-34300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-33400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-32500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-31600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-30900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-29300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-27100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-24900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-22600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-20200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-16000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-13700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-8600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-7200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5232,14 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5309,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5386,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,68 +5463,74 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F76" s="3">
         <v>3600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>6100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>7000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>11100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>11700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>15300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>16600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5540,14 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,95 +5617,107 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-900</v>
       </c>
       <c r="G81" s="3">
         <v>-900</v>
@@ -5336,58 +5726,64 @@
         <v>-900</v>
       </c>
       <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,31 +5809,33 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="F83" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>200</v>
@@ -5467,25 +5865,31 @@
         <v>200</v>
       </c>
       <c r="T83" s="3">
+        <v>200</v>
+      </c>
+      <c r="U83" s="3">
+        <v>200</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5959,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +6036,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +6113,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +6190,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6267,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-900</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-700</v>
       </c>
       <c r="H89" s="3">
         <v>-700</v>
       </c>
       <c r="I89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-2200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-1400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,31 +6377,33 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -5970,19 +6412,19 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>-200</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -5999,17 +6441,23 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6527,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,8 +6604,14 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6183,16 +6643,16 @@
         <v>-100</v>
       </c>
       <c r="M94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="N94" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="O94" s="3">
         <v>-200</v>
       </c>
       <c r="P94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Q94" s="3">
         <v>-200</v>
@@ -6201,28 +6661,34 @@
         <v>-200</v>
       </c>
       <c r="S94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-800</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,31 +6714,33 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6319,8 +6787,14 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6864,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6941,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,102 +7018,114 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>1900</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>12800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>1900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>4800</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6674,75 +7172,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-700</v>
+        <v>-600</v>
       </c>
       <c r="E102" s="3">
-        <v>-1000</v>
+        <v>-800</v>
       </c>
       <c r="F102" s="3">
         <v>-700</v>
       </c>
       <c r="G102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I102" s="3">
         <v>-800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-2700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>12300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>1900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-2200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,121 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -787,22 +790,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="3">
         <v>100</v>
       </c>
       <c r="J8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K8" s="3">
         <v>200</v>
       </c>
       <c r="L8" s="3">
+        <v>200</v>
+      </c>
+      <c r="M8" s="3">
         <v>300</v>
-      </c>
-      <c r="M8" s="3">
-        <v>200</v>
       </c>
       <c r="N8" s="3">
         <v>200</v>
@@ -811,34 +814,34 @@
         <v>200</v>
       </c>
       <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
-      </c>
-      <c r="S8" s="3">
-        <v>100</v>
       </c>
       <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
+      <c r="Y8" s="3">
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
@@ -846,8 +849,11 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -923,8 +929,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -941,17 +950,17 @@
         <v>0</v>
       </c>
       <c r="H10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3">
         <v>100</v>
       </c>
       <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,22 +1041,23 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
       </c>
       <c r="G12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H12" s="3">
         <v>300</v>
@@ -1055,8 +1068,8 @@
       <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
+      <c r="K12" s="3">
+        <v>300</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
@@ -1088,26 +1101,29 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3">
         <v>100</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X12" s="3">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3">
         <v>200</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1199,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1209,8 +1228,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1260,13 +1279,16 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1278,17 +1300,17 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1337,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1388,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E17" s="3">
         <v>900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1000</v>
       </c>
       <c r="H17" s="3">
         <v>1000</v>
       </c>
       <c r="I17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2400</v>
-      </c>
-      <c r="O17" s="3">
-        <v>2500</v>
       </c>
       <c r="P17" s="3">
         <v>2500</v>
       </c>
       <c r="Q17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="R17" s="3">
         <v>2100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2200</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-2300</v>
       </c>
       <c r="S18" s="3">
         <v>-2300</v>
       </c>
       <c r="T18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U18" s="3">
         <v>-1500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-2800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1578,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1566,8 +1599,8 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1602,11 +1635,11 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1614,8 +1647,8 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1623,8 +1656,11 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1632,76 +1668,79 @@
         <v>-900</v>
       </c>
       <c r="E21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-2100</v>
       </c>
       <c r="S21" s="3">
         <v>-2100</v>
       </c>
       <c r="T21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="U21" s="3">
         <v>-1300</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>-2400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1720,20 +1759,20 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1754,14 +1793,14 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>3600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,22 +1816,25 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-900</v>
       </c>
       <c r="H23" s="3">
         <v>-900</v>
@@ -1804,58 +1846,61 @@
         <v>-900</v>
       </c>
       <c r="K23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-2300</v>
       </c>
       <c r="S23" s="3">
         <v>-2300</v>
       </c>
       <c r="T23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U23" s="3">
         <v>-5100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1880,8 +1925,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1931,8 +1976,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,22 +2056,25 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
       </c>
       <c r="H26" s="3">
         <v>-900</v>
@@ -2035,72 +2086,75 @@
         <v>-900</v>
       </c>
       <c r="K26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-2300</v>
       </c>
       <c r="S26" s="3">
         <v>-2300</v>
       </c>
       <c r="T26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U26" s="3">
         <v>-5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
       </c>
       <c r="H27" s="3">
         <v>-900</v>
@@ -2112,58 +2166,61 @@
         <v>-900</v>
       </c>
       <c r="K27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L27" s="3">
         <v>-700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-2300</v>
       </c>
       <c r="S27" s="3">
         <v>-2300</v>
       </c>
       <c r="T27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U27" s="3">
         <v>-5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2536,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2490,8 +2559,8 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2526,11 +2595,11 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2538,8 +2607,8 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2547,22 +2616,25 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
       </c>
       <c r="H33" s="3">
         <v>-900</v>
@@ -2574,58 +2646,61 @@
         <v>-900</v>
       </c>
       <c r="K33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-2300</v>
       </c>
       <c r="S33" s="3">
         <v>-2300</v>
       </c>
       <c r="T33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U33" s="3">
         <v>-5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,22 +2776,25 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
       </c>
       <c r="H35" s="3">
         <v>-900</v>
@@ -2728,140 +2806,146 @@
         <v>-900</v>
       </c>
       <c r="K35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-2300</v>
       </c>
       <c r="S35" s="3">
         <v>-2300</v>
       </c>
       <c r="T35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U35" s="3">
         <v>-5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,71 +3003,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,8 +3081,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,25 +3161,28 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
         <v>0</v>
@@ -3099,13 +3191,13 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
       </c>
       <c r="M43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3117,26 +3209,26 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3149,8 +3241,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3175,8 +3270,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3226,8 +3321,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3252,45 +3350,45 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>600</v>
       </c>
       <c r="N45" s="3">
         <v>600</v>
       </c>
       <c r="O45" s="3">
+        <v>600</v>
+      </c>
+      <c r="P45" s="3">
         <v>800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,71 +3401,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>8500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3380,8 +3481,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3406,8 +3510,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3457,8 +3561,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3514,14 +3621,14 @@
         <v>100</v>
       </c>
       <c r="U48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V48" s="3">
+        <v>0</v>
+      </c>
+      <c r="W48" s="3">
         <v>100</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,16 +3641,19 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>600</v>
+      </c>
+      <c r="E49" s="3">
         <v>700</v>
-      </c>
-      <c r="E49" s="3">
-        <v>600</v>
       </c>
       <c r="F49" s="3">
         <v>600</v>
@@ -3552,28 +3662,28 @@
         <v>600</v>
       </c>
       <c r="H49" s="3">
+        <v>600</v>
+      </c>
+      <c r="I49" s="3">
         <v>700</v>
-      </c>
-      <c r="I49" s="3">
-        <v>800</v>
       </c>
       <c r="J49" s="3">
         <v>800</v>
       </c>
       <c r="K49" s="3">
+        <v>800</v>
+      </c>
+      <c r="L49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1200</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1300</v>
       </c>
       <c r="P49" s="3">
         <v>1300</v>
@@ -3582,13 +3692,13 @@
         <v>1300</v>
       </c>
       <c r="R49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="S49" s="3">
         <v>1400</v>
       </c>
       <c r="T49" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="U49" s="3">
         <v>1300</v>
@@ -3596,8 +3706,8 @@
       <c r="V49" s="3">
         <v>1300</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
+      <c r="W49" s="3">
+        <v>1300</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
@@ -3611,8 +3721,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3881,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3791,8 +3910,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3821,14 +3940,14 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3">
+        <v>0</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -3842,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,71 +4041,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>18200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3996,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,8 +4183,9 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4063,10 +4193,10 @@
         <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
         <v>100</v>
@@ -4084,40 +4214,40 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
       </c>
       <c r="Q57" s="3">
+        <v>200</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>100</v>
       </c>
       <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>100</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4131,8 +4261,11 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4188,11 +4321,11 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>2000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4208,19 +4341,22 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
         <v>0</v>
@@ -4229,50 +4365,50 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4285,25 +4421,28 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E60" s="3">
         <v>800</v>
       </c>
       <c r="F60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G60" s="3">
         <v>200</v>
       </c>
       <c r="H60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I60" s="3">
         <v>300</v>
@@ -4312,44 +4451,44 @@
         <v>300</v>
       </c>
       <c r="K60" s="3">
+        <v>300</v>
+      </c>
+      <c r="L60" s="3">
         <v>400</v>
-      </c>
-      <c r="L60" s="3">
-        <v>700</v>
       </c>
       <c r="M60" s="3">
         <v>700</v>
       </c>
       <c r="N60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O60" s="3">
         <v>800</v>
       </c>
       <c r="P60" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>700</v>
-      </c>
-      <c r="R60" s="3">
-        <v>1000</v>
       </c>
       <c r="S60" s="3">
         <v>1000</v>
       </c>
       <c r="T60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U60" s="3">
         <v>1600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,8 +4501,11 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4439,8 +4581,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4465,8 +4610,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4516,8 +4661,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,25 +4901,28 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E66" s="3">
         <v>800</v>
       </c>
       <c r="F66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="G66" s="3">
         <v>200</v>
       </c>
       <c r="H66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I66" s="3">
         <v>300</v>
@@ -4774,44 +4931,44 @@
         <v>300</v>
       </c>
       <c r="K66" s="3">
+        <v>300</v>
+      </c>
+      <c r="L66" s="3">
         <v>400</v>
-      </c>
-      <c r="L66" s="3">
-        <v>700</v>
       </c>
       <c r="M66" s="3">
         <v>700</v>
       </c>
       <c r="N66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O66" s="3">
         <v>800</v>
       </c>
       <c r="P66" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q66" s="3">
         <v>1100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>700</v>
-      </c>
-      <c r="R66" s="3">
-        <v>1000</v>
       </c>
       <c r="S66" s="3">
         <v>1000</v>
       </c>
       <c r="T66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U66" s="3">
         <v>1600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>600</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4824,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,71 +5331,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-38700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-37800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-35200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-34300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-33400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-32500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-31600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-30900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-29300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-24900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-20200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-16000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-13700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-8600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-7200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5238,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,71 +5651,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5546,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,104 +5811,110 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
       </c>
       <c r="H81" s="3">
         <v>-900</v>
@@ -5732,58 +5926,61 @@
         <v>-900</v>
       </c>
       <c r="K81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-2300</v>
       </c>
       <c r="S81" s="3">
         <v>-2300</v>
       </c>
       <c r="T81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="U81" s="3">
         <v>-5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6008,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5820,14 +6018,14 @@
         <v>0</v>
       </c>
       <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
         <v>-500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
@@ -5838,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>200</v>
@@ -5871,16 +6069,16 @@
         <v>200</v>
       </c>
       <c r="V83" s="3">
+        <v>200</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>100</v>
       </c>
       <c r="X83" s="3">
         <v>100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>100</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
@@ -5888,8 +6086,11 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,25 +6486,28 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
-      </c>
-      <c r="H89" s="3">
-        <v>-700</v>
       </c>
       <c r="I89" s="3">
         <v>-700</v>
@@ -6300,58 +6516,61 @@
         <v>-700</v>
       </c>
       <c r="K89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q89" s="3">
         <v>-1200</v>
       </c>
       <c r="R89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,16 +6598,17 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -6396,17 +6616,17 @@
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
@@ -6418,17 +6638,17 @@
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -6447,8 +6667,8 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
@@ -6456,8 +6676,11 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6836,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6649,13 +6878,13 @@
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-200</v>
       </c>
       <c r="R94" s="3">
         <v>-200</v>
@@ -6667,28 +6896,31 @@
         <v>-200</v>
       </c>
       <c r="U94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-800</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6742,8 +6975,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6793,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7266,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7044,8 +7289,8 @@
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -7054,23 +7299,23 @@
         <v>0</v>
       </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
@@ -7078,22 +7323,22 @@
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>12800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>4800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
+      <c r="Y100" s="3">
+        <v>0</v>
       </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
@@ -7101,8 +7346,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7127,8 +7375,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7178,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>12300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,124 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,22 +797,22 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3">
         <v>100</v>
       </c>
       <c r="K8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L8" s="3">
         <v>200</v>
       </c>
       <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
         <v>300</v>
-      </c>
-      <c r="N8" s="3">
-        <v>200</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
@@ -817,34 +821,34 @@
         <v>200</v>
       </c>
       <c r="Q8" s="3">
+        <v>200</v>
+      </c>
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200</v>
-      </c>
-      <c r="T8" s="3">
-        <v>100</v>
       </c>
       <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="V8" s="3">
         <v>100</v>
       </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
+      <c r="Z8" s="3">
+        <v>0</v>
       </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
@@ -852,8 +856,11 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -932,8 +939,11 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -953,17 +963,17 @@
         <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
       </c>
       <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1012,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1051,16 +1065,16 @@
         <v>200</v>
       </c>
       <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
       </c>
       <c r="G12" s="3">
         <v>200</v>
       </c>
       <c r="H12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I12" s="3">
         <v>300</v>
@@ -1071,8 +1085,8 @@
       <c r="K12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
+      <c r="L12" s="3">
+        <v>300</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
@@ -1104,26 +1118,29 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3">
         <v>100</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,8 +1219,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1231,8 +1251,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1282,17 +1302,20 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
@@ -1300,20 +1323,20 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1000</v>
       </c>
       <c r="I17" s="3">
         <v>1000</v>
       </c>
       <c r="J17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2400</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2500</v>
       </c>
       <c r="Q17" s="3">
         <v>2500</v>
       </c>
       <c r="R17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="S17" s="3">
         <v>2100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2200</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-2300</v>
       </c>
       <c r="T18" s="3">
         <v>-2300</v>
       </c>
       <c r="U18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V18" s="3">
         <v>-1500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-2800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,8 +1612,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1602,8 +1636,8 @@
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1638,11 +1672,11 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
-        <v>0</v>
+      <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1650,8 +1684,8 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1659,88 +1693,94 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-900</v>
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
         <v>-900</v>
       </c>
       <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-2100</v>
       </c>
       <c r="T21" s="3">
         <v>-2100</v>
       </c>
       <c r="U21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="V21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>-2400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1762,20 +1802,20 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1796,14 +1836,14 @@
         <v>0</v>
       </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>3600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1819,25 +1859,28 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-900</v>
       </c>
       <c r="I23" s="3">
         <v>-900</v>
@@ -1849,58 +1892,61 @@
         <v>-900</v>
       </c>
       <c r="L23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M23" s="3">
         <v>-700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-2300</v>
       </c>
       <c r="T23" s="3">
         <v>-2300</v>
       </c>
       <c r="U23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V23" s="3">
         <v>-5100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1928,8 +1974,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1979,8 +2025,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,25 +2108,28 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-900</v>
       </c>
       <c r="I26" s="3">
         <v>-900</v>
@@ -2089,75 +2141,78 @@
         <v>-900</v>
       </c>
       <c r="L26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M26" s="3">
         <v>-700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-2300</v>
       </c>
       <c r="T26" s="3">
         <v>-2300</v>
       </c>
       <c r="U26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V26" s="3">
         <v>-5100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-900</v>
       </c>
       <c r="I27" s="3">
         <v>-900</v>
@@ -2169,58 +2224,61 @@
         <v>-900</v>
       </c>
       <c r="L27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M27" s="3">
         <v>-700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-2300</v>
       </c>
       <c r="T27" s="3">
         <v>-2300</v>
       </c>
       <c r="U27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V27" s="3">
         <v>-5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,8 +2606,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2562,8 +2632,8 @@
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2598,11 +2668,11 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
-        <v>0</v>
+      <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -2610,8 +2680,8 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2619,25 +2689,28 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-900</v>
       </c>
       <c r="I33" s="3">
         <v>-900</v>
@@ -2649,58 +2722,61 @@
         <v>-900</v>
       </c>
       <c r="L33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M33" s="3">
         <v>-700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-2300</v>
       </c>
       <c r="T33" s="3">
         <v>-2300</v>
       </c>
       <c r="U33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V33" s="3">
         <v>-5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,25 +2855,28 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-900</v>
       </c>
       <c r="I35" s="3">
         <v>-900</v>
@@ -2809,143 +2888,149 @@
         <v>-900</v>
       </c>
       <c r="L35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M35" s="3">
         <v>-700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-2300</v>
       </c>
       <c r="T35" s="3">
         <v>-2300</v>
       </c>
       <c r="U35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V35" s="3">
         <v>-5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,74 +3090,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>13700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,8 +3171,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3164,28 +3254,31 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
         <v>0</v>
@@ -3194,13 +3287,13 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M43" s="3">
         <v>100</v>
       </c>
       <c r="N43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
@@ -3212,26 +3305,26 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3244,8 +3337,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3273,8 +3369,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3324,8 +3420,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3353,45 +3452,45 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>600</v>
       </c>
       <c r="O45" s="3">
         <v>600</v>
       </c>
       <c r="P45" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>100</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,74 +3503,77 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,8 +3586,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3513,8 +3618,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3564,13 +3669,16 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3">
         <v>100</v>
@@ -3624,14 +3732,14 @@
         <v>100</v>
       </c>
       <c r="V48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W48" s="3">
+        <v>0</v>
+      </c>
+      <c r="X48" s="3">
         <v>100</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3644,8 +3752,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3653,10 +3764,10 @@
         <v>600</v>
       </c>
       <c r="E49" s="3">
+        <v>600</v>
+      </c>
+      <c r="F49" s="3">
         <v>700</v>
-      </c>
-      <c r="F49" s="3">
-        <v>600</v>
       </c>
       <c r="G49" s="3">
         <v>600</v>
@@ -3665,28 +3776,28 @@
         <v>600</v>
       </c>
       <c r="I49" s="3">
+        <v>600</v>
+      </c>
+      <c r="J49" s="3">
         <v>700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>800</v>
       </c>
       <c r="K49" s="3">
         <v>800</v>
       </c>
       <c r="L49" s="3">
+        <v>800</v>
+      </c>
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1200</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1300</v>
       </c>
       <c r="Q49" s="3">
         <v>1300</v>
@@ -3695,13 +3806,13 @@
         <v>1300</v>
       </c>
       <c r="S49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="T49" s="3">
         <v>1400</v>
       </c>
       <c r="U49" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="V49" s="3">
         <v>1300</v>
@@ -3709,8 +3820,8 @@
       <c r="W49" s="3">
         <v>1300</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>1300</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,8 +4001,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3913,8 +4033,8 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -3943,14 +4063,14 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,74 +4167,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4800</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,22 +4314,23 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
@@ -4217,40 +4348,40 @@
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>400</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
-      </c>
-      <c r="V57" s="3">
-        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+      <c r="X57" s="3">
+        <v>100</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -4264,8 +4395,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4324,11 +4458,11 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>2000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4344,8 +4478,11 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4355,11 +4492,11 @@
       <c r="E59" s="3">
         <v>0</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>0</v>
@@ -4368,50 +4505,50 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
       </c>
       <c r="L59" s="3">
+        <v>100</v>
+      </c>
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>500</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,28 +4561,31 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>200</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
-      </c>
-      <c r="E60" s="3">
-        <v>800</v>
       </c>
       <c r="F60" s="3">
         <v>800</v>
       </c>
       <c r="G60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H60" s="3">
         <v>200</v>
       </c>
       <c r="I60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J60" s="3">
         <v>300</v>
@@ -4454,44 +4594,44 @@
         <v>300</v>
       </c>
       <c r="L60" s="3">
+        <v>300</v>
+      </c>
+      <c r="M60" s="3">
         <v>400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>700</v>
       </c>
       <c r="N60" s="3">
         <v>700</v>
       </c>
       <c r="O60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="P60" s="3">
         <v>800</v>
       </c>
       <c r="Q60" s="3">
+        <v>800</v>
+      </c>
+      <c r="R60" s="3">
         <v>1100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>700</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1000</v>
       </c>
       <c r="T60" s="3">
         <v>1000</v>
       </c>
       <c r="U60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V60" s="3">
         <v>1600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,8 +4644,11 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4584,8 +4727,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4613,8 +4759,8 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,28 +5059,31 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200</v>
+      </c>
+      <c r="E66" s="3">
         <v>900</v>
-      </c>
-      <c r="E66" s="3">
-        <v>800</v>
       </c>
       <c r="F66" s="3">
         <v>800</v>
       </c>
       <c r="G66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="H66" s="3">
         <v>200</v>
       </c>
       <c r="I66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J66" s="3">
         <v>300</v>
@@ -4934,44 +5092,44 @@
         <v>300</v>
       </c>
       <c r="L66" s="3">
+        <v>300</v>
+      </c>
+      <c r="M66" s="3">
         <v>400</v>
-      </c>
-      <c r="M66" s="3">
-        <v>700</v>
       </c>
       <c r="N66" s="3">
         <v>700</v>
       </c>
       <c r="O66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="P66" s="3">
         <v>800</v>
       </c>
       <c r="Q66" s="3">
+        <v>800</v>
+      </c>
+      <c r="R66" s="3">
         <v>1100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>700</v>
-      </c>
-      <c r="S66" s="3">
-        <v>1000</v>
       </c>
       <c r="T66" s="3">
         <v>1000</v>
       </c>
       <c r="U66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V66" s="3">
         <v>1600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>600</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,74 +5505,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-38700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-37800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-35200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-34300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-33400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-32500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-31600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-30900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-29300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-22600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-20200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-16000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-13700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-7200</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,74 +5837,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4200</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,110 +6003,116 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-900</v>
       </c>
       <c r="I81" s="3">
         <v>-900</v>
@@ -5929,58 +6124,61 @@
         <v>-900</v>
       </c>
       <c r="L81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M81" s="3">
         <v>-700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-2300</v>
       </c>
       <c r="T81" s="3">
         <v>-2300</v>
       </c>
       <c r="U81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="V81" s="3">
         <v>-5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6021,14 +6220,14 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>-500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -6039,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>200</v>
@@ -6072,16 +6271,16 @@
         <v>200</v>
       </c>
       <c r="W83" s="3">
+        <v>200</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>100</v>
       </c>
       <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
+      <c r="Z83" s="3">
+        <v>100</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>3</v>
@@ -6089,8 +6288,11 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,28 +6703,31 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
-      </c>
-      <c r="I89" s="3">
-        <v>-700</v>
       </c>
       <c r="J89" s="3">
         <v>-700</v>
@@ -6519,58 +6736,61 @@
         <v>-700</v>
       </c>
       <c r="L89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-1200</v>
       </c>
       <c r="R89" s="3">
         <v>-1200</v>
       </c>
       <c r="S89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6610,8 +6831,8 @@
       <c r="E91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -6619,17 +6840,17 @@
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
@@ -6641,17 +6862,17 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -6670,8 +6891,8 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>3</v>
@@ -6679,8 +6900,11 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,8 +7066,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6881,13 +7111,13 @@
         <v>-100</v>
       </c>
       <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-200</v>
       </c>
       <c r="S94" s="3">
         <v>-200</v>
@@ -6899,28 +7129,31 @@
         <v>-200</v>
       </c>
       <c r="V94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-800</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6978,8 +7212,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,13 +7512,16 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>3100</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -7292,8 +7538,8 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7302,23 +7548,23 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>1900</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>2500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
@@ -7326,22 +7572,22 @@
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>12800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>4800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
@@ -7349,8 +7595,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7378,8 +7627,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7429,84 +7678,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>12300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -1311,7 +1311,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1702,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-600</v>
+        <v>-700</v>
       </c>
       <c r="E21" s="3">
         <v>-900</v>
@@ -6214,7 +6214,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,147 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>100</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -814,22 +817,22 @@
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>100</v>
       </c>
       <c r="N8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
       </c>
       <c r="P8" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q8" s="3">
         <v>300</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>200</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
@@ -838,34 +841,34 @@
         <v>200</v>
       </c>
       <c r="T8" s="3">
+        <v>200</v>
+      </c>
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>200</v>
-      </c>
-      <c r="W8" s="3">
-        <v>100</v>
       </c>
       <c r="X8" s="3">
         <v>100</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="Y8" s="3">
         <v>100</v>
       </c>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="AA8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
+      <c r="AC8" s="3">
+        <v>0</v>
       </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
@@ -873,8 +876,11 @@
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -962,8 +968,11 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,7 +983,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -992,17 +1001,17 @@
         <v>0</v>
       </c>
       <c r="L10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M10" s="3">
         <v>100</v>
       </c>
       <c r="N10" s="3">
+        <v>100</v>
+      </c>
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1051,8 +1060,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,16 +1096,17 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
         <v>100</v>
-      </c>
-      <c r="E12" s="3">
-        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
@@ -1102,16 +1115,16 @@
         <v>200</v>
       </c>
       <c r="H12" s="3">
+        <v>200</v>
+      </c>
+      <c r="I12" s="3">
         <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>200</v>
       </c>
       <c r="J12" s="3">
         <v>200</v>
       </c>
       <c r="K12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L12" s="3">
         <v>300</v>
@@ -1122,8 +1135,8 @@
       <c r="N12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
+      <c r="O12" s="3">
+        <v>300</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
@@ -1155,26 +1168,29 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="3">
         <v>100</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,20 +1278,23 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,8 +1319,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1351,8 +1370,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1366,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1378,20 +1400,20 @@
         <v>0</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
       <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
         <v>500</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,97 +1495,101 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>900</v>
+      </c>
+      <c r="E17" s="3">
         <v>800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1500</v>
-      </c>
-      <c r="K17" s="3">
-        <v>1000</v>
       </c>
       <c r="L17" s="3">
         <v>1000</v>
       </c>
       <c r="M17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N17" s="3">
         <v>1100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2400</v>
-      </c>
-      <c r="S17" s="3">
-        <v>2500</v>
       </c>
       <c r="T17" s="3">
         <v>2500</v>
       </c>
       <c r="U17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="V17" s="3">
         <v>2100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1568,88 +1597,91 @@
         <v>-700</v>
       </c>
       <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-2300</v>
       </c>
       <c r="W18" s="3">
         <v>-2300</v>
       </c>
       <c r="X18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,8 +1713,9 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1713,8 +1746,8 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1749,11 +1782,11 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
@@ -1761,8 +1794,8 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>0</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1770,8 +1803,11 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,88 +1815,91 @@
         <v>-700</v>
       </c>
       <c r="E21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I21" s="3">
         <v>-900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="I21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-700</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-900</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-2100</v>
       </c>
       <c r="W21" s="3">
         <v>-2100</v>
       </c>
       <c r="X21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1891,20 +1930,20 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1925,14 +1964,14 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>3600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1948,34 +1987,37 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-900</v>
       </c>
       <c r="L23" s="3">
         <v>-900</v>
@@ -1987,58 +2029,61 @@
         <v>-900</v>
       </c>
       <c r="O23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P23" s="3">
         <v>-700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-2300</v>
       </c>
       <c r="W23" s="3">
         <v>-2300</v>
       </c>
       <c r="X23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2075,8 +2120,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -2126,8 +2171,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,34 +2263,37 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-900</v>
       </c>
       <c r="L26" s="3">
         <v>-900</v>
@@ -2254,84 +2305,87 @@
         <v>-900</v>
       </c>
       <c r="O26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P26" s="3">
         <v>-700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-2300</v>
       </c>
       <c r="W26" s="3">
         <v>-2300</v>
       </c>
       <c r="X26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-900</v>
       </c>
       <c r="L27" s="3">
         <v>-900</v>
@@ -2343,58 +2397,61 @@
         <v>-900</v>
       </c>
       <c r="O27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P27" s="3">
         <v>-700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-2300</v>
       </c>
       <c r="W27" s="3">
         <v>-2300</v>
       </c>
       <c r="X27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,8 +2815,11 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2781,8 +2850,8 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2817,11 +2886,11 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -2829,8 +2898,8 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -2838,34 +2907,37 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-900</v>
       </c>
       <c r="L33" s="3">
         <v>-900</v>
@@ -2877,58 +2949,61 @@
         <v>-900</v>
       </c>
       <c r="O33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P33" s="3">
         <v>-700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-2300</v>
       </c>
       <c r="W33" s="3">
         <v>-2300</v>
       </c>
       <c r="X33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,34 +3091,37 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-900</v>
       </c>
       <c r="L35" s="3">
         <v>-900</v>
@@ -3055,152 +3133,158 @@
         <v>-900</v>
       </c>
       <c r="O35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P35" s="3">
         <v>-700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-2300</v>
       </c>
       <c r="W35" s="3">
         <v>-2300</v>
       </c>
       <c r="X35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,83 +3350,84 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>13700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>16400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3354,8 +3440,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3443,8 +3532,11 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3457,23 +3549,23 @@
       <c r="F43" s="3">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+      <c r="G43" s="3">
+        <v>0</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3482,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
       </c>
       <c r="Q43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3500,26 +3592,26 @@
         <v>0</v>
       </c>
       <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
       <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
         <v>300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>400</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3624,11 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3570,8 +3665,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3621,8 +3716,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3659,45 +3757,45 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>600</v>
       </c>
       <c r="R45" s="3">
         <v>600</v>
       </c>
       <c r="S45" s="3">
+        <v>600</v>
+      </c>
+      <c r="T45" s="3">
         <v>800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3710,83 +3808,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>2500</v>
       </c>
       <c r="I46" s="3">
         <v>2500</v>
       </c>
       <c r="J46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K46" s="3">
         <v>3200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>11100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>14800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>16800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3400</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3799,8 +3900,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3837,8 +3941,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3888,8 +3992,11 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3903,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
@@ -3957,14 +4064,14 @@
         <v>100</v>
       </c>
       <c r="Y48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3">
         <v>100</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3977,28 +4084,31 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>500</v>
+      </c>
+      <c r="E49" s="3">
         <v>600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>500</v>
-      </c>
-      <c r="F49" s="3">
-        <v>600</v>
       </c>
       <c r="G49" s="3">
         <v>600</v>
       </c>
       <c r="H49" s="3">
+        <v>600</v>
+      </c>
+      <c r="I49" s="3">
         <v>700</v>
-      </c>
-      <c r="I49" s="3">
-        <v>600</v>
       </c>
       <c r="J49" s="3">
         <v>600</v>
@@ -4007,28 +4117,28 @@
         <v>600</v>
       </c>
       <c r="L49" s="3">
+        <v>600</v>
+      </c>
+      <c r="M49" s="3">
         <v>700</v>
-      </c>
-      <c r="M49" s="3">
-        <v>800</v>
       </c>
       <c r="N49" s="3">
         <v>800</v>
       </c>
       <c r="O49" s="3">
+        <v>800</v>
+      </c>
+      <c r="P49" s="3">
         <v>900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1200</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1300</v>
       </c>
       <c r="T49" s="3">
         <v>1300</v>
@@ -4037,13 +4147,13 @@
         <v>1300</v>
       </c>
       <c r="V49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="W49" s="3">
         <v>1400</v>
       </c>
       <c r="X49" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="Y49" s="3">
         <v>1300</v>
@@ -4051,8 +4161,8 @@
       <c r="Z49" s="3">
         <v>1300</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>3</v>
+      <c r="AA49" s="3">
+        <v>1300</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>3</v>
@@ -4066,8 +4176,11 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4360,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4255,8 +4374,8 @@
       <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="F52" s="3">
+        <v>100</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
@@ -4264,12 +4383,12 @@
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4282,8 +4401,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -4312,14 +4431,14 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>0</v>
       </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
@@ -4333,8 +4452,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,83 +4544,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>7300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>10800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>18200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4800</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4636,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,8 +4706,9 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4592,16 +4722,16 @@
         <v>0</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -4619,40 +4749,40 @@
         <v>100</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>400</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
       </c>
       <c r="U57" s="3">
+        <v>200</v>
+      </c>
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
+      <c r="AA57" s="3">
+        <v>100</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
@@ -4666,8 +4796,11 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4735,11 +4868,11 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>2000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4755,8 +4888,11 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4775,11 +4911,11 @@
       <c r="H59" s="3">
         <v>0</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -4788,50 +4924,50 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
       </c>
       <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>500</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4844,37 +4980,40 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E60" s="3">
         <v>400</v>
       </c>
       <c r="F60" s="3">
+        <v>400</v>
+      </c>
+      <c r="G60" s="3">
         <v>200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>800</v>
       </c>
       <c r="I60" s="3">
         <v>800</v>
       </c>
       <c r="J60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="K60" s="3">
         <v>200</v>
       </c>
       <c r="L60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M60" s="3">
         <v>300</v>
@@ -4883,44 +5022,44 @@
         <v>300</v>
       </c>
       <c r="O60" s="3">
+        <v>300</v>
+      </c>
+      <c r="P60" s="3">
         <v>400</v>
-      </c>
-      <c r="P60" s="3">
-        <v>700</v>
       </c>
       <c r="Q60" s="3">
         <v>700</v>
       </c>
       <c r="R60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="S60" s="3">
         <v>800</v>
       </c>
       <c r="T60" s="3">
+        <v>800</v>
+      </c>
+      <c r="U60" s="3">
         <v>1100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>700</v>
-      </c>
-      <c r="V60" s="3">
-        <v>1000</v>
       </c>
       <c r="W60" s="3">
         <v>1000</v>
       </c>
       <c r="X60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y60" s="3">
         <v>1600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4933,8 +5072,11 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5022,8 +5164,11 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5060,8 +5205,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -5111,8 +5256,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,37 +5532,40 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E66" s="3">
         <v>400</v>
       </c>
       <c r="F66" s="3">
+        <v>400</v>
+      </c>
+      <c r="G66" s="3">
         <v>200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>900</v>
-      </c>
-      <c r="H66" s="3">
-        <v>800</v>
       </c>
       <c r="I66" s="3">
         <v>800</v>
       </c>
       <c r="J66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="K66" s="3">
         <v>200</v>
       </c>
       <c r="L66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M66" s="3">
         <v>300</v>
@@ -5417,44 +5574,44 @@
         <v>300</v>
       </c>
       <c r="O66" s="3">
+        <v>300</v>
+      </c>
+      <c r="P66" s="3">
         <v>400</v>
-      </c>
-      <c r="P66" s="3">
-        <v>700</v>
       </c>
       <c r="Q66" s="3">
         <v>700</v>
       </c>
       <c r="R66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="S66" s="3">
         <v>800</v>
       </c>
       <c r="T66" s="3">
+        <v>800</v>
+      </c>
+      <c r="U66" s="3">
         <v>1100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
-      </c>
-      <c r="V66" s="3">
-        <v>1000</v>
       </c>
       <c r="W66" s="3">
         <v>1000</v>
       </c>
       <c r="X66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y66" s="3">
         <v>1600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>600</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,8 +5624,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,83 +6026,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-42800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-41500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-40500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-39900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-38700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-37800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-36700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-35200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-34300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-32500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-31600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-30900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-29300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-24900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-22600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-20200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-16000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-13700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-8600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-7200</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5945,8 +6118,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,83 +6394,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4200</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6301,8 +6486,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,128 +6578,134 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-900</v>
       </c>
       <c r="L81" s="3">
         <v>-900</v>
@@ -6523,58 +6717,61 @@
         <v>-900</v>
       </c>
       <c r="O81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="P81" s="3">
         <v>-700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-2300</v>
       </c>
       <c r="W81" s="3">
         <v>-2300</v>
       </c>
       <c r="X81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6618,23 +6816,23 @@
         <v>0</v>
       </c>
       <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
         <v>-300</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>-500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -6645,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>200</v>
@@ -6678,16 +6876,16 @@
         <v>200</v>
       </c>
       <c r="Z83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA83" s="3">
         <v>400</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>100</v>
       </c>
       <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+      <c r="AC83" s="3">
+        <v>100</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
@@ -6695,8 +6893,11 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,37 +7353,40 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="E89" s="3">
         <v>-400</v>
       </c>
       <c r="F89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G89" s="3">
         <v>-700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-700</v>
       </c>
       <c r="M89" s="3">
         <v>-700</v>
@@ -7179,58 +7395,61 @@
         <v>-700</v>
       </c>
       <c r="O89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-1200</v>
       </c>
       <c r="U89" s="3">
         <v>-1200</v>
       </c>
       <c r="V89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7481,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7282,8 +7502,8 @@
       <c r="H91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -7291,17 +7511,17 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P91" s="3">
         <v>-100</v>
@@ -7313,17 +7533,17 @@
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
@@ -7342,8 +7562,8 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
@@ -7351,8 +7571,11 @@
       <c r="AE91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,13 +7755,16 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
@@ -7580,13 +7809,13 @@
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-200</v>
       </c>
       <c r="V94" s="3">
         <v>-200</v>
@@ -7598,28 +7827,31 @@
         <v>-200</v>
       </c>
       <c r="Y94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-800</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7689,8 +7922,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7740,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,23 +8249,26 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8039,8 +8284,8 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -8049,23 +8294,23 @@
         <v>0</v>
       </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>2500</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>1400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
@@ -8073,22 +8318,22 @@
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>12800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>4800</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
@@ -8096,8 +8341,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8134,8 +8382,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8185,93 +8433,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="E102" s="3">
         <v>-500</v>
       </c>
       <c r="F102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G102" s="3">
         <v>2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AMST_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="92">
   <si>
     <t>AMST</t>
   </si>
@@ -656,144 +656,148 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43555</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
-        <v>100</v>
+      <c r="D8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E8" s="3">
         <v>100</v>
@@ -802,7 +806,7 @@
         <v>100</v>
       </c>
       <c r="G8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -820,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="M8" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3">
         <v>100</v>
       </c>
       <c r="O8" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P8" s="3">
         <v>200</v>
       </c>
       <c r="Q8" s="3">
+        <v>200</v>
+      </c>
+      <c r="R8" s="3">
         <v>300</v>
-      </c>
-      <c r="R8" s="3">
-        <v>200</v>
       </c>
       <c r="S8" s="3">
         <v>200</v>
@@ -844,34 +848,34 @@
         <v>200</v>
       </c>
       <c r="U8" s="3">
+        <v>200</v>
+      </c>
+      <c r="V8" s="3">
         <v>100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>200</v>
-      </c>
-      <c r="X8" s="3">
-        <v>100</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="3">
+      <c r="Z8" s="3">
         <v>100</v>
       </c>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="AB8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
+      <c r="AD8" s="3">
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
@@ -879,8 +883,11 @@
       <c r="AF8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -971,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,7 +996,7 @@
         <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -1004,17 +1014,17 @@
         <v>0</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1063,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,19 +1110,20 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3">
         <v>200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>200</v>
       </c>
       <c r="G12" s="3">
         <v>200</v>
@@ -1118,16 +1132,16 @@
         <v>200</v>
       </c>
       <c r="I12" s="3">
+        <v>200</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
-      </c>
-      <c r="J12" s="3">
-        <v>200</v>
       </c>
       <c r="K12" s="3">
         <v>200</v>
       </c>
       <c r="L12" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M12" s="3">
         <v>300</v>
@@ -1138,8 +1152,8 @@
       <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>300</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
@@ -1171,26 +1185,29 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB12" s="3">
         <v>100</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1292,12 +1312,12 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1322,8 +1342,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1373,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1403,20 +1426,20 @@
         <v>0</v>
       </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
       <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
         <v>500</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1465,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,100 +1522,104 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>800</v>
+      </c>
+      <c r="E17" s="3">
         <v>900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
-      </c>
-      <c r="L17" s="3">
-        <v>1000</v>
       </c>
       <c r="M17" s="3">
         <v>1000</v>
       </c>
       <c r="N17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2400</v>
-      </c>
-      <c r="T17" s="3">
-        <v>2500</v>
       </c>
       <c r="U17" s="3">
         <v>2500</v>
       </c>
       <c r="V17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="W17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1600,88 +1630,91 @@
         <v>-700</v>
       </c>
       <c r="F18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1800</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-2300</v>
       </c>
       <c r="X18" s="3">
         <v>-2300</v>
       </c>
       <c r="Y18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,8 +1747,9 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1749,8 +1783,8 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1785,11 +1819,11 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
@@ -1797,8 +1831,8 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
+      <c r="AD20" s="3">
+        <v>0</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
@@ -1806,8 +1840,11 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1818,88 +1855,91 @@
         <v>-700</v>
       </c>
       <c r="F21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G21" s="3">
         <v>-900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-2100</v>
       </c>
       <c r="X21" s="3">
         <v>-2100</v>
       </c>
       <c r="Y21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1933,20 +1973,20 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1967,14 +2007,14 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>3600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1990,8 +2030,11 @@
       <c r="AF22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1999,28 +2042,28 @@
         <v>-700</v>
       </c>
       <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-900</v>
       </c>
       <c r="M23" s="3">
         <v>-900</v>
@@ -2032,58 +2075,61 @@
         <v>-900</v>
       </c>
       <c r="P23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-2300</v>
       </c>
       <c r="X23" s="3">
         <v>-2300</v>
       </c>
       <c r="Y23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2123,8 +2169,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2174,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,8 +2315,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2275,28 +2327,28 @@
         <v>-700</v>
       </c>
       <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-900</v>
       </c>
       <c r="M26" s="3">
         <v>-900</v>
@@ -2308,58 +2360,61 @@
         <v>-900</v>
       </c>
       <c r="P26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-2300</v>
       </c>
       <c r="X26" s="3">
         <v>-2300</v>
       </c>
       <c r="Y26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2367,28 +2422,28 @@
         <v>-700</v>
       </c>
       <c r="E27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-900</v>
       </c>
       <c r="M27" s="3">
         <v>-900</v>
@@ -2400,58 +2455,61 @@
         <v>-900</v>
       </c>
       <c r="P27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-2300</v>
       </c>
       <c r="X27" s="3">
         <v>-2300</v>
       </c>
       <c r="Y27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,8 +2885,11 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2853,8 +2923,8 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2889,11 +2959,11 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
@@ -2901,8 +2971,8 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
+      <c r="AD32" s="3">
+        <v>0</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
@@ -2910,8 +2980,11 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2919,28 +2992,28 @@
         <v>-700</v>
       </c>
       <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-900</v>
       </c>
       <c r="M33" s="3">
         <v>-900</v>
@@ -2952,58 +3025,61 @@
         <v>-900</v>
       </c>
       <c r="P33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-2300</v>
       </c>
       <c r="X33" s="3">
         <v>-2300</v>
       </c>
       <c r="Y33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,8 +3170,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3103,28 +3182,28 @@
         <v>-700</v>
       </c>
       <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-900</v>
       </c>
       <c r="M35" s="3">
         <v>-900</v>
@@ -3136,155 +3215,161 @@
         <v>-900</v>
       </c>
       <c r="P35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-2300</v>
       </c>
       <c r="X35" s="3">
         <v>-2300</v>
       </c>
       <c r="Y35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43555</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,86 +3437,87 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>13700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,8 +3530,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3535,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3552,23 +3645,23 @@
       <c r="G43" s="3">
         <v>0</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
+      <c r="H43" s="3">
+        <v>0</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3577,13 +3670,13 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="3">
         <v>100</v>
       </c>
       <c r="R43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
@@ -3595,26 +3688,26 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
       <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
         <v>300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3627,8 +3720,11 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3668,8 +3764,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3719,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3760,45 +3859,45 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>600</v>
       </c>
       <c r="S45" s="3">
         <v>600</v>
       </c>
       <c r="T45" s="3">
+        <v>600</v>
+      </c>
+      <c r="U45" s="3">
         <v>800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3811,86 +3910,89 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1400</v>
-      </c>
-      <c r="I46" s="3">
-        <v>2500</v>
       </c>
       <c r="J46" s="3">
         <v>2500</v>
       </c>
       <c r="K46" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L46" s="3">
         <v>3200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>10800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>11100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>12800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>14800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3400</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3903,8 +4005,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3944,8 +4049,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3995,8 +4100,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4013,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3">
         <v>100</v>
@@ -4067,14 +4175,14 @@
         <v>100</v>
       </c>
       <c r="Z48" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="3">
         <v>100</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4087,8 +4195,11 @@
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4096,22 +4207,22 @@
         <v>500</v>
       </c>
       <c r="E49" s="3">
+        <v>500</v>
+      </c>
+      <c r="F49" s="3">
         <v>600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>600</v>
       </c>
       <c r="H49" s="3">
         <v>600</v>
       </c>
       <c r="I49" s="3">
+        <v>600</v>
+      </c>
+      <c r="J49" s="3">
         <v>700</v>
-      </c>
-      <c r="J49" s="3">
-        <v>600</v>
       </c>
       <c r="K49" s="3">
         <v>600</v>
@@ -4120,28 +4231,28 @@
         <v>600</v>
       </c>
       <c r="M49" s="3">
+        <v>600</v>
+      </c>
+      <c r="N49" s="3">
         <v>700</v>
-      </c>
-      <c r="N49" s="3">
-        <v>800</v>
       </c>
       <c r="O49" s="3">
         <v>800</v>
       </c>
       <c r="P49" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q49" s="3">
         <v>900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1200</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1300</v>
       </c>
       <c r="U49" s="3">
         <v>1300</v>
@@ -4150,13 +4261,13 @@
         <v>1300</v>
       </c>
       <c r="W49" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="X49" s="3">
         <v>1400</v>
       </c>
       <c r="Y49" s="3">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="Z49" s="3">
         <v>1300</v>
@@ -4164,8 +4275,8 @@
       <c r="AA49" s="3">
         <v>1300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>3</v>
+      <c r="AB49" s="3">
+        <v>1300</v>
       </c>
       <c r="AC49" s="3" t="s">
         <v>3</v>
@@ -4179,8 +4290,11 @@
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4377,8 +4497,8 @@
       <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
+      <c r="G52" s="3">
+        <v>100</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -4386,12 +4506,12 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4404,8 +4524,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -4434,14 +4554,14 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>0</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
@@ -4455,8 +4575,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,86 +4670,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>7300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4639,8 +4765,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4725,16 +4856,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
@@ -4752,40 +4883,40 @@
         <v>100</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>400</v>
-      </c>
-      <c r="T57" s="3">
-        <v>200</v>
       </c>
       <c r="U57" s="3">
         <v>200</v>
       </c>
       <c r="V57" s="3">
+        <v>200</v>
+      </c>
+      <c r="W57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>100</v>
       </c>
       <c r="AA57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
+      <c r="AB57" s="3">
+        <v>100</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
@@ -4799,8 +4930,11 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4871,11 +5005,11 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>2000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4891,8 +5025,11 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4914,11 +5051,11 @@
       <c r="I59" s="3">
         <v>0</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -4927,50 +5064,50 @@
         <v>0</v>
       </c>
       <c r="N59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O59" s="3">
         <v>100</v>
       </c>
       <c r="P59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>500</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4983,40 +5120,43 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>200</v>
+      </c>
+      <c r="E60" s="3">
         <v>500</v>
-      </c>
-      <c r="E60" s="3">
-        <v>400</v>
       </c>
       <c r="F60" s="3">
         <v>400</v>
       </c>
       <c r="G60" s="3">
+        <v>400</v>
+      </c>
+      <c r="H60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>800</v>
       </c>
       <c r="J60" s="3">
         <v>800</v>
       </c>
       <c r="K60" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="L60" s="3">
         <v>200</v>
       </c>
       <c r="M60" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N60" s="3">
         <v>300</v>
@@ -5025,44 +5165,44 @@
         <v>300</v>
       </c>
       <c r="P60" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q60" s="3">
         <v>400</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>700</v>
       </c>
       <c r="R60" s="3">
         <v>700</v>
       </c>
       <c r="S60" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="T60" s="3">
         <v>800</v>
       </c>
       <c r="U60" s="3">
+        <v>800</v>
+      </c>
+      <c r="V60" s="3">
         <v>1100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>700</v>
-      </c>
-      <c r="W60" s="3">
-        <v>1000</v>
       </c>
       <c r="X60" s="3">
         <v>1000</v>
       </c>
       <c r="Y60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5075,8 +5215,11 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5167,8 +5310,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5208,8 +5354,8 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -5259,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,40 +5690,43 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200</v>
+      </c>
+      <c r="E66" s="3">
         <v>500</v>
-      </c>
-      <c r="E66" s="3">
-        <v>400</v>
       </c>
       <c r="F66" s="3">
         <v>400</v>
       </c>
       <c r="G66" s="3">
+        <v>400</v>
+      </c>
+      <c r="H66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>800</v>
       </c>
       <c r="J66" s="3">
         <v>800</v>
       </c>
       <c r="K66" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="L66" s="3">
         <v>200</v>
       </c>
       <c r="M66" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N66" s="3">
         <v>300</v>
@@ -5577,44 +5735,44 @@
         <v>300</v>
       </c>
       <c r="P66" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q66" s="3">
         <v>400</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>700</v>
       </c>
       <c r="R66" s="3">
         <v>700</v>
       </c>
       <c r="S66" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="T66" s="3">
         <v>800</v>
       </c>
       <c r="U66" s="3">
+        <v>800</v>
+      </c>
+      <c r="V66" s="3">
         <v>1100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
-      </c>
-      <c r="W66" s="3">
-        <v>1000</v>
       </c>
       <c r="X66" s="3">
         <v>1000</v>
       </c>
       <c r="Y66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z66" s="3">
         <v>1600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5627,8 +5785,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5937,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,86 +6200,89 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-43500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-42800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-42100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-41500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-40500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-37800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-36700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-35200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-34300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-32500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-30900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-29300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-24900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-22600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-20200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-18300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-13700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-7200</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6121,8 +6295,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,86 +6580,89 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E76" s="3">
         <v>1500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>11100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>11700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4200</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6489,8 +6675,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,105 +6770,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43555</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6687,28 +6882,28 @@
         <v>-700</v>
       </c>
       <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-900</v>
       </c>
       <c r="M81" s="3">
         <v>-900</v>
@@ -6720,58 +6915,61 @@
         <v>-900</v>
       </c>
       <c r="P81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1900</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-2300</v>
       </c>
       <c r="X81" s="3">
         <v>-2300</v>
       </c>
       <c r="Y81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6819,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -6828,14 +7027,14 @@
         <v>0</v>
       </c>
       <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>-500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -6846,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>200</v>
@@ -6879,16 +7078,16 @@
         <v>200</v>
       </c>
       <c r="AA83" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB83" s="3">
         <v>400</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>100</v>
       </c>
       <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>100</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
@@ -6896,8 +7095,11 @@
       <c r="AF83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,40 +7570,43 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
-      </c>
-      <c r="E89" s="3">
-        <v>-400</v>
       </c>
       <c r="F89" s="3">
         <v>-400</v>
       </c>
       <c r="G89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H89" s="3">
         <v>-700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-700</v>
       </c>
       <c r="N89" s="3">
         <v>-700</v>
@@ -7398,58 +7615,61 @@
         <v>-700</v>
       </c>
       <c r="P89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-1200</v>
       </c>
       <c r="V89" s="3">
         <v>-1200</v>
       </c>
       <c r="W89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="X89" s="3">
         <v>-1300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7505,8 +7726,8 @@
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7514,17 +7735,17 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q91" s="3">
         <v>-100</v>
@@ -7536,17 +7757,17 @@
         <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
@@ -7565,8 +7786,8 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
+      <c r="AD91" s="3">
+        <v>0</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>3</v>
@@ -7574,8 +7795,11 @@
       <c r="AF91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,16 +7985,19 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
@@ -7812,13 +8042,13 @@
         <v>-100</v>
       </c>
       <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-200</v>
       </c>
       <c r="W94" s="3">
         <v>-200</v>
@@ -7830,28 +8060,31 @@
         <v>-200</v>
       </c>
       <c r="Z94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-800</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7925,8 +8159,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7976,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8263,15 +8509,15 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>3100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8287,8 +8533,8 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -8297,23 +8543,23 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>1900</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>2500</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
@@ -8321,22 +8567,22 @@
         <v>0</v>
       </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>12800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4800</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
+      <c r="AD100" s="3">
+        <v>0</v>
       </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
@@ -8344,8 +8590,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8385,8 +8634,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -8436,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-500</v>
       </c>
       <c r="F102" s="3">
         <v>-500</v>
       </c>
       <c r="G102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H102" s="3">
         <v>2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>12300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
